--- a/02_Scraping_longchau_playwright/products.xlsx
+++ b/02_Scraping_longchau_playwright/products.xlsx
@@ -1,34 +1,502 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Le Nhat Tung\Documents\GitHub\osds_2627\02_Scraping_longchau_playwright\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DBD18D-580B-46AE-9A45-7D4689DAF581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="21164" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="153">
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>price_text</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>original_price</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-ho-tro-cai-thien-suc-de-khang-cho-co-the-zincelite-vitamins-for-life-30-v.html</t>
+  </si>
+  <si>
+    <t>Viên uống hỗ trợ cải thiện sức đề kháng cho cơ thể ZINCELITE Vitamins For Life (Hộp 30 viên)</t>
+  </si>
+  <si>
+    <t>00051537</t>
+  </si>
+  <si>
+    <t>295.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/vien_uong_ho_tro_cai_thien_suc_de_khang_cho_co_the_zincelite_30v_vitamins_for_life_00051537_5_3219e03dca.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/siro-ho-tro-hap-thu-canxi-giup-xuong-rang-chac-khoe-nature-s-way-kids-smart-drops-vitamin-d3-k2-11-ml.html</t>
+  </si>
+  <si>
+    <t>Siro hỗ trợ hấp thu canxi, giúp xương, răng chắc khỏe Nature's Way Kids Smart Drops Vitamin D3+K2 (Hộp 11ml)</t>
+  </si>
+  <si>
+    <t>00051046</t>
+  </si>
+  <si>
+    <t>360.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/siro_ho_tro_hap_thu_canxi_giup_xuong_rang_chac_khoe_11ml_natures_way_kids_smart_drops_vitamin_d3_k2_00051046_6_19800cf1e0.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-ho-tro-giam-met-moi-active-nerves-new-nordic-30-v.html</t>
+  </si>
+  <si>
+    <t>Viên uống hỗ trợ giảm mệt mỏi New Nordic Active Nerves New Nordic (30 viên)</t>
+  </si>
+  <si>
+    <t>00050680</t>
+  </si>
+  <si>
+    <t>468.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_00557_e2078cd02c.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/nature-s-way-kids-smart-liquid-zinc-100-ml.html</t>
+  </si>
+  <si>
+    <t>Siro bổ sung kẽm và hỗ trợ kích thích thèm ăn Kids Smart Liquid Zinc Nature's Way (Hộp 100ml)</t>
+  </si>
+  <si>
+    <t>00049574</t>
+  </si>
+  <si>
+    <t>355.500đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_01175_3608a08456.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/bo-sung-vitamin-d3-ho-tro-xuong-rang-d3-drops-dao-nordic-health-10-ml.html</t>
+  </si>
+  <si>
+    <t>Dung dịch hỗ trợ phát triển xương, răng cho trẻ D3 Drops DAO Nordic Health (10ml)</t>
+  </si>
+  <si>
+    <t>00047382</t>
+  </si>
+  <si>
+    <t>225.600đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_01841_7ea3c478cf.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-bo-sung-vitamin-va-khoang-chat-easylife-immuvita-100-v.html</t>
+  </si>
+  <si>
+    <t>Viên uống bổ sung vitamin và khoáng chất cho cơ thể, tăng sức khỏe Immuvita Easylife (100 viên)</t>
+  </si>
+  <si>
+    <t>00045954</t>
+  </si>
+  <si>
+    <t>410.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_05505_4c243a16f9.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/siro-bo-sung-canxi-d3-k2-kingphar-6-x5-ong.html</t>
+  </si>
+  <si>
+    <t>Siro bổ sung canxi &amp; vitamin D3, K2 cho cơ thể Canxi-D3-K2 Kingphar (6 vỉ x 5 ống x 5ml)</t>
+  </si>
+  <si>
+    <t>00045449</t>
+  </si>
+  <si>
+    <t>115.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_04874_6c29236c37.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/siro-brauer-baby-kids-d3-k2-high-potency-mk-7-drops-10-ml.html</t>
+  </si>
+  <si>
+    <t>Siro giúp xương răng chắc khỏe, bổ sung vitamin D3 + K2 Brauer Baby &amp; Kids D3 + K2 High Potency MK-7 Drops (10ml)</t>
+  </si>
+  <si>
+    <t>00045391</t>
+  </si>
+  <si>
+    <t>316.800đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_04996_7d25dc3860.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-ho-tro-nao-bo-thi-luc-va-suc-khoe-tim-mach-omega-3-plus-kenko-120-v.html</t>
+  </si>
+  <si>
+    <t>Viên uống bổ sung Omega 3 hỗ trợ não, thị lực và tim mạch OMEGA 3 PLUS Kenko (120 viên)</t>
+  </si>
+  <si>
+    <t>00045384</t>
+  </si>
+  <si>
+    <t>920.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_05020_ce6da165fb.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-bo-sung-omega-3-6-9-premium-omexxel-100-v.html</t>
+  </si>
+  <si>
+    <t>Viên uống hỗ trợ tốt cho não và mắt Omexxel 3-6-9 Premium (100 viên)</t>
+  </si>
+  <si>
+    <t>00045364</t>
+  </si>
+  <si>
+    <t>362.400đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_09384_b9a30a1717.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-nhai-ho-tro-su-phat-trien-xuong-cho-tre-em-borne-mineral-new-nordic-120-v.html</t>
+  </si>
+  <si>
+    <t>Viên nhai giúp tăng chiều cao, giảm nguy cơ còi xương cho trẻ em Borne Mineral New Nordic (120 viên)</t>
+  </si>
+  <si>
+    <t>00043230</t>
+  </si>
+  <si>
+    <t>657.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_08913_afa4db8279.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuc-pham-chuc-nang/vien-uong-bo-sung-canxi-giam-nguy-co-loang-xuong-calcium-premium-jpanwell-120-v.html</t>
+  </si>
+  <si>
+    <t>Viên bổ sung canxi, khoáng chất giảm nguy cơ loãng xương Calcium Premium JpanWell (120 viên)</t>
+  </si>
+  <si>
+    <t>00040747</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_09985_6ae3f52230.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/eugica-vien-uong-dieu-tri-ho-cam-cum-490.html</t>
+  </si>
+  <si>
+    <t>Thuốc Eugica MEGA We care điều trị ho đờm, cảm cúm, sổ mũi (10 vỉ x 10 viên)</t>
+  </si>
+  <si>
+    <t>00010253</t>
+  </si>
+  <si>
+    <t>730đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_04536_e077afde79.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/berocca-1515.html</t>
+  </si>
+  <si>
+    <t>Viên sủi Berocca Bayer bổ sung vitamin và khoáng chất (10 viên)</t>
+  </si>
+  <si>
+    <t>00009723</t>
+  </si>
+  <si>
+    <t>75.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/IMG_1758_33831b7cab.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/kremils-s-3315.html</t>
+  </si>
+  <si>
+    <t>Viên nhai Kremil-S United điều trị đau dạ dày, giảm nóng rát dạ dày, ợ nóng, ợ chua (10 vỉ x 10 viên)</t>
+  </si>
+  <si>
+    <t>00004244</t>
+  </si>
+  <si>
+    <t>1.200đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/vien_nhai_kremil_s_10_vi_x_10_vien_united_00004244_3936ef2f24.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/farzincol-10mg-3786.html</t>
+  </si>
+  <si>
+    <t>Thuốc Farzincol Pharmedic điều trị thiếu kẽm (10 vỉ x 10 viên)</t>
+  </si>
+  <si>
+    <t>00002990</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/farzincol_10mg_10x10_pharmedic_00002990_60f2647dea.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/smecta-2236.html</t>
+  </si>
+  <si>
+    <t>Thuốc bột pha hỗn dịch uống Smecta Ipsen hương cam &amp; vani điều trị tiêu chảy, bảo vệ niêm mạc tiêu hoá (30 gói)</t>
+  </si>
+  <si>
+    <t>00006780</t>
+  </si>
+  <si>
+    <t>5.100đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/00006780_Smecta_68b17d7625.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/differin-0130mg-17372.html</t>
+  </si>
+  <si>
+    <t>Kem Differin Galderma điều trị mụn trứng cá (30g)</t>
+  </si>
+  <si>
+    <t>00002441</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/differin_0_1_cream_galderma_30g_00002441_1_07c5a0e7d8.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/clorpheniramin-4-200v-4228.html</t>
+  </si>
+  <si>
+    <t>Thuốc Clorpheniramin 4 DHG điều trị viêm mũi dị ứng, chảy nước mũi (10 vỉ x 20 viên)</t>
+  </si>
+  <si>
+    <t>00001954</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/clorpheniramin_4mg_10x20_dhg_00001954_12cfe441d7.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/klenzit-15g-3330.html</t>
+  </si>
+  <si>
+    <t>Gel bôi da Klenzit MS điều trị mụn trứng cá (15g)</t>
+  </si>
+  <si>
+    <t>00004206</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/IMG_4396_43605a2469.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/thuoc/efferalgan-500mg-1620.html</t>
+  </si>
+  <si>
+    <t>Viên sủi Efferalgan 500mg UPSA SAS giảm đau, hạ sốt (4 vỉ x 4 viên)</t>
+  </si>
+  <si>
+    <t>00008350</t>
+  </si>
+  <si>
+    <t>51.990đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/eferalgan_1_f94f787f4f.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/duoc-my-pham/gel-rua-mat-teenilicious-lam-sach-mun-loai-bo-bui-ban-va-ba-nhon-ngan-ngua-mun-hop-60-g.html</t>
+  </si>
+  <si>
+    <t>Gel rửa mặt ngừa mụn, sạch bã nhờn Teenilicious 60g</t>
+  </si>
+  <si>
+    <t>00049302</t>
+  </si>
+  <si>
+    <t>166.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_09119_4be9757d50.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/duoc-my-pham/kem-chong-nang-sac-ngoc-khang-spf-50-pa-nang-tone-nhe-danh-cho-moi-loai-da-50-g.html</t>
+  </si>
+  <si>
+    <t>Kem chống nắng nâng tông nhẹ Sắc Ngọc Khang SPF 50+ PA++++ 50g</t>
+  </si>
+  <si>
+    <t>00048912</t>
+  </si>
+  <si>
+    <t>195.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_09535_10bb3d35c9.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/duoc-my-pham/mieng-dan-mun-elaband-hydro-dot-tea-tree-23-mieng.html</t>
+  </si>
+  <si>
+    <t>Miếng dán mụn Elaband Hydrodot Teatree (23 miếng) hút dịch mụn, giảm sưng viêm</t>
+  </si>
+  <si>
+    <t>00048487</t>
+  </si>
+  <si>
+    <t>64.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_02973_36520645dc.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/duoc-my-pham/fixderma-shadow-spf-55-gel-75-g-kem-chong-nang-and-duong-am.html</t>
+  </si>
+  <si>
+    <t>Gel chống nắng Fixderma Shadow SPF 55+ bảo vệ da khỏi tia UV, dưỡng ẩm (75g)</t>
+  </si>
+  <si>
+    <t>00048435</t>
+  </si>
+  <si>
+    <t>314.300đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_02779_df52c5e191.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/duoc-my-pham/pax-moly-blemish-care-30-ml-orange-tinh-chat-duong-da-giup-da-mem-min-duong-am-lam-sang-da-mo-tham-nam-tan-nhang.html</t>
+  </si>
+  <si>
+    <t>Tinh chất dưỡng ẩm, sáng da Pax Moly Blemish Care (orange) 30ml</t>
+  </si>
+  <si>
+    <t>00048409</t>
+  </si>
+  <si>
+    <t>210.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/DSC_02730_4bbf2f9697.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/trang-thiet-bi-y-te/bot-phu-dang-xit-cicasilver-spray-125-ml-bao-ve-lam-lanh-vet-thuong-ho.html</t>
+  </si>
+  <si>
+    <t>Xịt phủ vết thương, vết bỏng Cicasilver Spray 125ml giúp bảo vệ làm lành vết thương</t>
+  </si>
+  <si>
+    <t>00049463</t>
+  </si>
+  <si>
+    <t>590.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/xit_phu_vet_thuong_vet_bong_cicasilver_spray_125ml_00049463_1_7f06546b43.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/trang-thiet-bi-y-te/mieng-dan-ha-sot-bye-bye-fever-super-cool-3-goi-x-2-mieng-dung-cho-tre-tu-10-tuoi-va-nguoi-lon.html</t>
+  </si>
+  <si>
+    <t>Miếng dán hạ sốt ByeBye Fever Super Cool dùng cho trẻ từ 10 tuổi và người lớn (3 gói x 2 miếng)</t>
+  </si>
+  <si>
+    <t>00049379</t>
+  </si>
+  <si>
+    <t>60.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/mieng_dan_ha_sot_3_goi_x_2_mieng_byebye_fever_super_cool_hisamitsu_00049379_1_47236f8b9c.png</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/trang-thiet-bi-y-te/urgo-family-2-cm-x-6-cm-bang-ca-nhan-5-5-mieng.html</t>
+  </si>
+  <si>
+    <t>Băng cá nhân Urgo Family 2x6cm (10 miếng)</t>
+  </si>
+  <si>
+    <t>00503671</t>
+  </si>
+  <si>
+    <t>16.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/IMG_0096_5c029ed8e7.jpg</t>
+  </si>
+  <si>
+    <t>https://nhathuoclongchau.com.vn/trang-thiet-bi-y-te/mieng-dan-ha-sot-lion-hiepita-for-baby-6-goi-x-2-mieng-0-2-tuoi.html</t>
+  </si>
+  <si>
+    <t>Miếng dán hạ sốt Lion Hiepita for baby dùng cho trẻ từ 0-2 tuổi (6 gói x 2 miếng)</t>
+  </si>
+  <si>
+    <t>00503071</t>
+  </si>
+  <si>
+    <t>130.000đ</t>
+  </si>
+  <si>
+    <t>https://cdn.nhathuoclongchau.com.vn/v1/static/mieng_dan_ha_sot_lion_hiepita_for_baby_6_goi_x_2_mieng_00503071_1_d1348b04b3.png</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +515,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,14 +817,640 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultColWidth="17.5" defaultRowHeight="14.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="100.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>295000</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>360000</v>
+      </c>
+      <c r="F3">
+        <v>40000010</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4">
+        <v>468000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>355500</v>
+      </c>
+      <c r="F5">
+        <v>39500010</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>225600</v>
+      </c>
+      <c r="F6">
+        <v>28200020</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>410000</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>115000</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>316800</v>
+      </c>
+      <c r="F9">
+        <v>39600020</v>
+      </c>
+      <c r="G9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>920000</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11">
+        <v>362400</v>
+      </c>
+      <c r="F11">
+        <v>45300020</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12">
+        <v>657000</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13">
+        <v>920000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14">
+        <v>730</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15">
+        <v>75000</v>
+      </c>
+      <c r="G15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16">
+        <v>1200</v>
+      </c>
+      <c r="G16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18">
+        <v>5100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22">
+        <v>51990</v>
+      </c>
+      <c r="G22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23">
+        <v>166000</v>
+      </c>
+      <c r="G23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24">
+        <v>195000</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25">
+        <v>64000</v>
+      </c>
+      <c r="F25">
+        <v>8000020</v>
+      </c>
+      <c r="G25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26">
+        <v>314300</v>
+      </c>
+      <c r="F26">
+        <v>44900030</v>
+      </c>
+      <c r="G26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27">
+        <v>210000</v>
+      </c>
+      <c r="F27">
+        <v>30000030</v>
+      </c>
+      <c r="G27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28">
+        <v>590000</v>
+      </c>
+      <c r="G28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29">
+        <v>60000</v>
+      </c>
+      <c r="G29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30">
+        <v>16000</v>
+      </c>
+      <c r="G30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31">
+        <v>130000</v>
+      </c>
+      <c r="G31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>